--- a/artfynd/A 10218-2024 artfynd.xlsx
+++ b/artfynd/A 10218-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110367522</v>
+        <v>110367624</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>769282.6900524817</v>
+        <v>769283</v>
       </c>
       <c r="R2" t="n">
-        <v>7449104.311298216</v>
+        <v>7449125</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110367065</v>
+        <v>110367915</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769325.5721835425</v>
+        <v>769253</v>
       </c>
       <c r="R3" t="n">
-        <v>7449116.063148073</v>
+        <v>7449123</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,24 +852,14 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På 80 cm högstubbe med brandljud på två sidor av stubben</t>
+          <t>Högstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110368347</v>
+        <v>110367065</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769252.5097526573</v>
+        <v>769326</v>
       </c>
       <c r="R4" t="n">
-        <v>7449122.908180862</v>
+        <v>7449116</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,24 +958,14 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högstubbe med brandljud och kottsmedja</t>
+          <t>På 80 cm högstubbe med brandljud på två sidor av stubben</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,42 +993,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110367915</v>
+        <v>110369654</v>
       </c>
       <c r="B5" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769252.5097526573</v>
+        <v>769134</v>
       </c>
       <c r="R5" t="n">
-        <v>7449122.908180862</v>
+        <v>7449071</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,33 +1065,22 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Högstubbe med brandljud</t>
+          <t>En begynnande gråfura där bark lossnat och flera hackade hål nertill på stammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1152,49 +1092,45 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Ann Dewall</t>
+          <t>Vivi Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110367624</v>
+        <v>110367755</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769283.3167932328</v>
+        <v>769259</v>
       </c>
       <c r="R6" t="n">
-        <v>7449125.593670457</v>
+        <v>7449123</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,24 +1171,9 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På högstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,43 +1201,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110367755</v>
+        <v>110367522</v>
       </c>
       <c r="B7" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769259.5590993788</v>
+        <v>769283</v>
       </c>
       <c r="R7" t="n">
-        <v>7449123.219611259</v>
+        <v>7449104</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,19 +1272,14 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På högstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110369654</v>
+        <v>110368347</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,27 +1318,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1441,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769134.1405200365</v>
+        <v>769253</v>
       </c>
       <c r="R8" t="n">
-        <v>7449071.394600455</v>
+        <v>7449123</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,32 +1378,23 @@
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-26</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En begynnande gråfura där bark lossnat och flera hackade hål nertill på stammen</t>
+          <t>På högstubbe med brandljud och kottsmedja</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Vivi Eriksson</t>
+          <t>Vivi Eriksson, Ann Dewall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
